--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="424">
   <si>
     <t>id</t>
   </si>
@@ -4657,6 +4657,75 @@
 Yeah
 Finally found it
 It's mine</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>人間界方面</t>
+  </si>
+  <si>
+    <t>Toward the Human World</t>
+  </si>
+  <si>
+    <t>26.09.10</t>
+  </si>
+  <si>
+    <t>人間界へ行くには
+このエスカレーターに乗る
+別に珍しいものじゃない
+毎朝みんな
+ここから仕事へ向かう
+ゴウンゴウン
+乗っている間に
+体は少しずつ人間へ変わっていく
+鱗が消えて
+腕が二本になって
+目も二つになる
+上にいた頃はあんな姿だった連中も
+下へ着く頃には立派な会社員だ
+私ももう十年以上使っている
+ネクタイまで勝手に出てくるから
+なかなか便利なものだ
+ただ
+たまに変換の遅いやつがいる
+おいまだ尻尾残ってるぞ
+え
+本当ですか
+まあいい
+ズボンに入れとけ
+遅刻するぞ
+……
+今日も人間界は朝から忙しいのだ</t>
+  </si>
+  <si>
+    <t>To get to the human world,
+you take this escalator.
+It’s nothing unusual.
+Every morning,
+everyone heads to work from here.
+Rumble, rumble.
+As you ride,
+your body gradually transforms into a human one.
+Your scales disappear.
+Your arms become two.
+Your eyes become two.
+Even those who looked like that up above
+are perfectly respectable office workers by the time they reach the bottom.
+I’ve been using it myself for over ten years now.
+It even gives you a necktie automatically,
+so it’s pretty convenient.
+Though sometimes,
+you get someone whose transformation is a little slow.
+Hey,
+you’ve still got a tail.
+Huh?
+Really?
+Ah, whatever.
+Just tuck it into your pants.
+You’re gonna be late.
+...
+Another busy morning in the human world.</t>
   </si>
 </sst>
 </file>
@@ -7715,12 +7784,24 @@
       <c r="Y71" s="3"/>
     </row>
     <row r="72">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
+      <c r="A72" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>423</v>
+      </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="430">
   <si>
     <t>id</t>
   </si>
@@ -4726,6 +4726,102 @@
 You’re gonna be late.
 ...
 Another busy morning in the human world.</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>人類保護区</t>
+  </si>
+  <si>
+    <t>Human Reserve</t>
+  </si>
+  <si>
+    <t>26.09.17</t>
+  </si>
+  <si>
+    <t>「人類は絶滅させてはならない。
+しかし、文明を持たせてもならない。」
+それが彼らの決めたルールだ
+人類が地球を壊しかけたあの日から
+二万年以上が経った
+今では我々も
+洞窟での暮らしにすっかり慣れた
+食料は毎朝ここで配給される
+病気になれば治してくれるし
+危険な生物も近づいてこない
+昔よりずっと安全らしい
+ただし
+文明を使うには彼らの許可がいる
+火
+文字
+農耕
+車輪
+人間が昔使っていたものを
+一つずつ申請する
+申請に使えるのは
+戦争を生き残ったこの端末だけだ
+カタカタ
+お
+車輪の申請どうだった？
+まだ審査中
+今年こそ通ると思ったんだけどな
+無理だろ
+去年
+隣の集落が二輪車作ったからな
+あれでまた百年延びたらしいぞ
+マジか
+一輪にしとけばよかったのにな
+……
+まあいい
+芋もらって帰ろう
+人類が火を取り戻すまで
+あと四百二十七年
+人類は今日も
+順調に保護されている</t>
+  </si>
+  <si>
+    <t>“Humanity must not be allowed to go extinct.
+But neither must it be allowed to have civilization.”
+That is the rule they established.
+More than twenty thousand years have passed
+since the day humanity nearly destroyed the Earth.
+By now,
+we’ve grown quite used to living in caves.
+Food is distributed here every morning.
+If we get sick, they heal us.
+Dangerous creatures are kept away.
+Apparently, life is much safer than it used to be.
+There is just one condition.
+To use anything from civilization,
+we need their permission.
+Fire.
+Writing.
+Agriculture.
+The wheel.
+Everything humans once used
+must be applied for, one by one.
+And this terminal,
+the only one that survived the war,
+is the only place we can submit an application.
+Clack clack.
+Hey.
+What happened with the application for the wheel?
+Still under review.
+I thought it might finally get approved this year.
+No chance.
+Last year,
+the settlement next door built a two-wheeled vehicle.
+Apparently that set us back another hundred years.
+Seriously?
+They should’ve just stuck with one wheel.
+...
+Oh well.
+Let’s get our potatoes and go home.
+Until humanity is allowed to use fire again:
+427 years.
+Humanity remains,
+as always, safely under protection.</t>
   </si>
 </sst>
 </file>
@@ -7823,12 +7919,24 @@
       <c r="Y72" s="3"/>
     </row>
     <row r="73">
-      <c r="A73" s="4"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
+      <c r="A73" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>429</v>
+      </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="436">
   <si>
     <t>id</t>
   </si>
@@ -4822,6 +4822,52 @@
 427 years.
 Humanity remains,
 as always, safely under protection.</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>ピーマンBeatbox</t>
+  </si>
+  <si>
+    <t>Bell Pepper Beatbox</t>
+  </si>
+  <si>
+    <t>26.09.20</t>
+  </si>
+  <si>
+    <t>時間はかかったが
+ようやく私のクローンが完成した
+完璧だ
+これなら街を歩いても
+誰も私のクローンだとは気づくまい
+ピーマン型ラボの中で
+男は秘密の研究を続けていた
+ヘリコプターが飛び
+巨大な操作の手が
+もうすぐそこまで伸びてきていることも知らず
+ドゥビドゥビドゥ
+ズッタッタウンタッタ
+ピーマン beatbox
+奇怪な愉快犯が
+今日も唸るのだ</t>
+  </si>
+  <si>
+    <t>It took some time,
+but at last, my clone is complete.
+Perfect.
+Now I can walk through the city
+and no one will ever know he’s my clone.
+Inside a bell pepper-shaped lab,
+the man continued his secret research.
+A helicopter flew overhead,
+unaware that a giant hand
+was already reaching in to manipulate him.
+Dooby-dooby-doo
+Zutta-tatta-unta-tta
+Bell Pepper Beatbox
+The bizarre prankster
+rumbles on again today.</t>
   </si>
 </sst>
 </file>
@@ -7958,12 +8004,24 @@
       <c r="Y73" s="3"/>
     </row>
     <row r="74">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
+      <c r="A74" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>435</v>
+      </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="454">
   <si>
     <t>id</t>
   </si>
@@ -4868,6 +4868,175 @@
 Bell Pepper Beatbox
 The bizarre prankster
 rumbles on again today.</t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>美妙</t>
+  </si>
+  <si>
+    <t>Strangely Delicious</t>
+  </si>
+  <si>
+    <t>26.09.22</t>
+  </si>
+  <si>
+    <t>くんくん
+確かこのあたりから香ってるんだけどな
+今日はセンサーが鈍い気がする
+まあ
+70年代のセンサーだから仕方ない
+私はモグラ型機械をゆっくり進めた
+この辺りは地上との距離が近い
+あ、いた
+店長へ連絡しておこう
+このサイズなら十人前にはなりそうだ
+...
+自分たちが普段垂れ流しているものが
+まさか食材になって地中にいるなんて
+人間達は考えもしないだろうな
+美味じゃなくて美妙なのだ、世界は
+食って
+出して
+また食っている</t>
+  </si>
+  <si>
+    <t>Sniff, sniff.
+I'm sure the smell is coming from around here.
+The sensor seems a little dull today.
+Well,
+it's from the '70s.Can't really blame it.
+I slowly moved the mole machine forward.
+We're pretty close to the surface around here.
+Ah, there it is.
+Better let the manager know.
+At this size,it should make about ten servings.
+...
+Humans would never imagine that what they casually let out every day
+ends up underground and becomes food.
+It's not just delicious.
+It's mysteriously delicious.
+The world
+eats,
+lets it out,
+and eats again.</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>あと8分</t>
+  </si>
+  <si>
+    <t>8 Minutes Left</t>
+  </si>
+  <si>
+    <t>26.09.24</t>
+  </si>
+  <si>
+    <t>あいつ今日も来てるな
+最近よく来ますね
+チップ読み取ってもらおっと
+え
+まだ入れてないの？
+はい
+なんだか怖くて
+総務から催促来てない？
+来てます
+三回来てます
+早く入れた方がいいぞ
+処理されちまうだろあいつみたいに
+...
+処理って
+…
+あと8分だ
+黙って食え</t>
+  </si>
+  <si>
+    <t>He’s here again today.
+He’s been coming around a lot lately.
+Maybe I’ll have him scan my chip.
+Huh?
+You still haven’t got one?
+No.
+I’m kind of scared.
+Hasn’t HR been reminding you?
+Yeah.
+Three times already.
+You’d better get one soon.
+You’ll get processed, just like that guy.
+...
+What do you mean by “processed”?
+…
+Eight minutes left.
+Shut up and eat.</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>眠る場所</t>
+  </si>
+  <si>
+    <t>The Place to Rest</t>
+  </si>
+  <si>
+    <t>26.09.26</t>
+  </si>
+  <si>
+    <t>大丈夫よ
+私は恐竜の頭にケーブルを繋いだ
+今日入力するのは死亡地点と埋没位置
+この個体は三十二年後
+ここから百二十キロ東で死ぬ
+右を下にして倒れ
+そのまま地中に埋まる
+七千万年以上経ったあと
+人間たちがこいつの骨を掘り出す
+周辺では昆虫型探査機が地層を調べている
+未来で発見された化石と
+同じ場所に埋まらなければならない
+ピピッ
+入力完了
+...
+私の時代だって同じようなもの
+今が辛いのも分かる
+でもね
+いつか先の未来の自分から
+今日の自分になんて声をかける？
+そこにいるのはほんの一瞬じゃない
+心配しないで
+ほら行ってらっしゃい
+三十二年後に眠る場所は
+もう見つけてあるから</t>
+  </si>
+  <si>
+    <t>Don’t worry.
+I connected a cable to the dinosaur’s head.
+Today’s input:the location of its death and where it will be buried.
+This one will die thirty-two years from now,
+120 kilometers east of here.
+It will fall on its right side
+and be buried there beneath the earth.
+More than seventy million years later,
+humans will dig up its bones.
+Around us,insect-like probes are surveying the geological layers.
+It has to be buried in the exact same place
+where its fossil will be discovered in the future.
+Beep.
+Input complete.
+...
+It’s much the same in my time.
+I know things are hard right now.
+But tell me—
+if your future self could look back at you today,
+what would they say?
+You’re only there for a moment, aren’t you?
+Don’t worry.
+Now, off you go.
+The place where you’ll rest thirty-two years from now
+has already been found.</t>
   </si>
 </sst>
 </file>
@@ -8043,12 +8212,24 @@
       <c r="Y74" s="3"/>
     </row>
     <row r="75">
-      <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+      <c r="A75" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
@@ -8070,12 +8251,24 @@
       <c r="Y75" s="3"/>
     </row>
     <row r="76">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
+      <c r="A76" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>447</v>
+      </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
@@ -8097,12 +8290,24 @@
       <c r="Y76" s="3"/>
     </row>
     <row r="77">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
+      <c r="A77" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>453</v>
+      </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="460">
   <si>
     <t>id</t>
   </si>
@@ -5037,6 +5037,81 @@
 Now, off you go.
 The place where you’ll rest thirty-two years from now
 has already been found.</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>人間設計課</t>
+  </si>
+  <si>
+    <t>Humanity Design Department</t>
+  </si>
+  <si>
+    <t>26.09.28</t>
+  </si>
+  <si>
+    <t>なぜだ
+なんで何回やってもこうなっちまうんだ
+お互い争いあって最後は自滅しちまう
+なんて人間は愚かなんだ
+週末ジョギングして
+夕方からラーメンとビール呑んでるだけで
+幸せじゃないのか？
+カタカタ
+私は人間の設計データを開いた
+これで何度目だ
+寿命を変えてみたり
+性格を変えてみたり
+欲を減らしてみたり
+色々やった
+それでもこいつらは
+こっちが考えもしなかったことを始める
+やっぱり
+俺のデザインが間違ってるんだろうな
+後ろにいた女が
+モニターを覗き込んだ
+焦りは禁物ですよ、サー
+我々の予測どおりに動く人間なんて作ってどうするんです？
+我々が欲しいのは予想だにしない動きをする
+アノーマルなデータなのです
+……
+そうか
+間違っているから
+だからいいのか
+魔界では今日も
+こんな議論が続いている</t>
+  </si>
+  <si>
+    <t>Why?
+Why does it always end up like this, no matter how many times I try?
+They fight each other,and in the end, they destroy themselves.
+Humans really are foolish.
+Wouldn't they be happy just going for a jog on the weekend,
+then having ramen and a beer in the evening?
+Clack clack.
+I opened the human design data.
+How many times has it been now?
+I've changed their lifespans,
+changed their personalities,
+reduced their desires.
+I've tried all sorts of things.
+And still,they always start doing things
+we never even imagined.
+I guess
+there really is something wrong with my design.
+The woman behind me
+leaned over and looked at the monitor.
+Don't rush it, sir.
+What would be the point of creating humans who behave exactly as we predict?
+What we need is anomalous data
+from behavior we could never anticipate.
+...
+I see.
+It's because they're flawed...
+that they're valuable.
+And so, even today,
+discussions like this continue in Makai.</t>
   </si>
 </sst>
 </file>
@@ -8329,12 +8404,24 @@
       <c r="Y77" s="3"/>
     </row>
     <row r="78">
-      <c r="A78" s="4"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
+      <c r="A78" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>459</v>
+      </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="472">
   <si>
     <t>id</t>
   </si>
@@ -5112,6 +5112,122 @@
 that they're valuable.
 And so, even today,
 discussions like this continue in Makai.</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
+    <t>瀬戸内ナンタルチア</t>
+  </si>
+  <si>
+    <t>Setouchi Nantaruchia</t>
+  </si>
+  <si>
+    <t>26.09.30</t>
+  </si>
+  <si>
+    <t>瀬戸内の潮風がこのラボには最適なのだ  
+海上500mに作られた  
+ナンタルチア  
+私が何をしているかだって？  
+それが私にもよく分からない  
+毎朝恒温槽から
+卵を三個取り出して食べる  
+あとは
+よくわからない数値を入力する  
+入社して十二年
+ずっとそれだけだ  
+君も似たようなもんだろう
+...
+パチ
+パチ
+パチ
+お  
+今日はよく瞬きするな  
+さあ  
+金魚に餌やって
+そろそろ帰るか</t>
+  </si>
+  <si>
+    <t>The sea breeze of the Seto Inland Sea is perfect for this lab  
+Five hundred meters above the sea
+stands Nantaruchia  
+You want to know what I do here?  
+Honestly I'm not really sure myself  
+Every morning
+I take three eggs from the incubator and eat them  
+Then I enter some numbers
+I don't really understand  
+I've been with the company for twelve years
+and that's pretty much all I've ever done  
+Your job's probably not that different  
+...  
+Blink
+Blink
+Blink  
+Oh  
+It's blinking a lot today  
+Well then  
+I'll feed the goldfish  
+and I guess it's about time to head home</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>るーるるる</t>
+  </si>
+  <si>
+    <t>Loo loo loo</t>
+  </si>
+  <si>
+    <t>26.10.1</t>
+  </si>
+  <si>
+    <t>るーるるる
+月面旅館へ初めて来た
+ここでは昔から立派な海老が獲れる
+地球では高級品だ
+今年も大きいですね
+立派な海老をありがとうございます
+いえいえこちらこそです
+男は私の方を見た
+ではそろそろ行きましょうか
+はい
+私は地球へ帰る社員たちに
+軽く頭を下げた
+まさか海老の引き換えとして
+僕を使っていただけるなんて光栄です
+...
+ところで僕は
+これから何をするんでしょうか
+男は海老の箱を見ながら言った
+大丈夫ですよ
+海老も最初は
+みんなそう言いますから</t>
+  </si>
+  <si>
+    <t>Loo loo loo
+It was my first time visiting the inn on the Moon
+They’ve been catching magnificent shrimp here
+for as long as anyone can remember Back on Earth
+they’re a luxury They’re big again this year
+Thank you for such magnificent shrimp
+No, no thank you
+The man looked at me
+Well then shall we get going?
+Yes
+I gave a slight bow
+to my coworkers heading back to Earth
+I’m honored
+that you’d take me in exchange for the shrimp
+...
+By the way
+what am I going to do from here?
+The man looked at the boxes of shrimp and said
+Don’t worry
+The shrimp all said
+the same thing at first</t>
   </si>
 </sst>
 </file>
@@ -8443,12 +8559,24 @@
       <c r="Y78" s="3"/>
     </row>
     <row r="79">
-      <c r="A79" s="4"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
+      <c r="A79" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>465</v>
+      </c>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
@@ -8470,12 +8598,24 @@
       <c r="Y79" s="3"/>
     </row>
     <row r="80">
-      <c r="A80" s="4"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
+      <c r="A80" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>471</v>
+      </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="478">
   <si>
     <t>id</t>
   </si>
@@ -5228,6 +5228,75 @@
 Don’t worry
 The shrimp all said
 the same thing at first</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>転生茶</t>
+  </si>
+  <si>
+    <t>Reincarnation Tea</t>
+  </si>
+  <si>
+    <t>26.10.2</t>
+  </si>
+  <si>
+    <t>人は死ぬと閻魔様のところへ行く
+生前の行いを審査され
+次の生へ送られるのだ
+ただごく稀に時空の狭間へ流される者がいる
+私もその一人だ
+気がつくと古い宇宙船の中に座っていた
+目の前には骸骨の店主
+次は人間へ？
+ああ
+人間になるのは初めてなのね
+店主は奥の培養槽から緑の液体を汲み上げた
+ここでは死者から抽出した記憶を混ぜ
+煎じて飲ませる
+いろんな人生を少しずつ混ぜるらしい
+これを全部飲んだら地球へ送ります
+苦いでしょう
+ただ
+初めてならそのくらいがいいですよ
+…
+あいや待て
+地球だったら
+もう少し後悔を入れておきましょう
+多くないですか？
+大丈夫
+人間だけ
+胎内から出る瞬間にフラッシュして
+全部忘れることになってますから
+-</t>
+  </si>
+  <si>
+    <t>When people die,they go before Enma, the Judge of the Dead.
+Their deeds in life are judged,
+and they are sent on to their next life.
+But every once in a while,someone drifts into the space between time and dimensions.
+I was one of them.
+When I came to,I was sitting inside an old spaceship.
+In front of me was a skeleton innkeeper.
+Human next?
+Ah.
+So this is your first time becoming human.
+The innkeeper scooped up some green liquid from a culture tank in the back.
+Here, memories extracted from the dead are blended together, brewed, and served to drink.
+Apparently, they mix in a little from all kinds of lives.
+Once you finish this,we'll send you to Earth.
+Bitter, isn't it?
+But for your first time,that's about right.
+...
+Oh, wait.
+If you're going to Earth,we'd better add a little more regret.
+Isn't that a bit much?
+Don't worry.
+Only humans.
+The moment they leave the womb,they're flashed
+and everything is wiped from their memory.
+That's how it works.</t>
   </si>
 </sst>
 </file>
@@ -8637,12 +8706,24 @@
       <c r="Y80" s="3"/>
     </row>
     <row r="81">
-      <c r="A81" s="4"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
+      <c r="A81" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>477</v>
+      </c>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="489">
   <si>
     <t>id</t>
   </si>
@@ -5242,7 +5242,7 @@
     <t>26.10.2</t>
   </si>
   <si>
-    <t>人は死ぬと閻魔様のところへ行く
+    <t xml:space="preserve">人は死ぬと閻魔様のところへ行く
 生前の行いを審査され
 次の生へ送られるのだ
 ただごく稀に時空の狭間へ流される者がいる
@@ -5269,7 +5269,7 @@
 人間だけ
 胎内から出る瞬間にフラッシュして
 全部忘れることになってますから
--</t>
+</t>
   </si>
   <si>
     <t>When people die,they go before Enma, the Judge of the Dead.
@@ -5297,6 +5297,110 @@
 The moment they leave the womb,they're flashed
 and everything is wiped from their memory.
 That's how it works.</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>海底の一杯</t>
+  </si>
+  <si>
+    <t>One Drink Under the Sea</t>
+  </si>
+  <si>
+    <t>26.10.5</t>
+  </si>
+  <si>
+    <t>ここには暗い客が集まる  
+自分なんてもうどうだっていい  
+毎晩濃い酒を一杯だけひっかける  
+今日も喉が焼ける  
+これがいい  
+仕事のことを忘れたい  
+店内には機械魚が泳いでいる  
+海底なんだから
+そんなものだと思っている  
+……  
+だが ここは海底ではなく
+水槽なのだ  
+機械魚は魚ではなく
+観測装置なのだ
+酒も
+店も
+仕事も
+家も  
+すべてあの方が用意した  
+実験は順調なのである</t>
+  </si>
+  <si>
+    <t>Here, the gloomy ones gather.
+I don't care what happens to me anymore.
+Every night, I knock back just one shot of strong liquor.
+It burns my throat again tonight.
+That's what I like.
+I just want to forget about work.
+Mechanical fish swim around inside the bar.
+I never think much of it.
+We're at the bottom of the sea, after all.
+...
+But this isn't the bottom of the sea.
+It's an aquarium.
+The mechanical fish aren't fish.
+They're observation devices.
+The liquor,
+the bar,
+the job,
+the home—
+all of it was prepared by Him.
+The experiment is proceeding smoothly.</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>森の黒薬</t>
+  </si>
+  <si>
+    <t>The Forest's Black Medicine</t>
+  </si>
+  <si>
+    <t>森へ虫を採りに行く
+幼虫でも昆虫でも構わない
+捕まえた虫を大鍋でじっくり煮る
+グツグツ
+と真っ黒な墨が出てくる
+その墨を鉄鍋へ移して
+水分がなくなるまで煎る
+あとは小さく丸めれば完成
+毎年冬になると
+私はこうして黒い錠剤を作る
+何の薬かって？
+知らないアル
+...
+ゴウン
+お今日も客が来たアル
+あいつら
+毎年来るから
+効いてるんじゃないか？</t>
+  </si>
+  <si>
+    <t>I head into the forest to gather bugs.
+Larvae, insects—anything will do.
+I toss whatever I catch into a big pot and let it simmer.
+Bubble, bubble.
+Soon, thick black ink starts to seep out.
+I pour the ink into an iron pan
+and roast it until all the moisture is gone.
+Then I roll it into little pills.
+Every winter,
+this is how I make my black pills.
+What kind of medicine is it?
+I don't know, aru.
+...
+Vrrrrmmm...
+Oh.Another customer today, aru.
+They come back every year.
+So I guess it must be working, right?</t>
   </si>
 </sst>
 </file>
@@ -8745,12 +8849,24 @@
       <c r="Y81" s="3"/>
     </row>
     <row r="82">
-      <c r="A82" s="4"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
+      <c r="A82" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>483</v>
+      </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
@@ -8772,12 +8888,24 @@
       <c r="Y82" s="3"/>
     </row>
     <row r="83">
-      <c r="A83" s="4"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
+      <c r="A83" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>488</v>
+      </c>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="500">
   <si>
     <t>id</t>
   </si>
@@ -5381,7 +5381,7 @@
 お今日も客が来たアル
 あいつら
 毎年来るから
-効いてるんじゃないか？</t>
+効いてるんじゃないか</t>
   </si>
   <si>
     <t>I head into the forest to gather bugs.
@@ -5401,6 +5401,100 @@
 Oh.Another customer today, aru.
 They come back every year.
 So I guess it must be working, right?</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>メディソンマン</t>
+  </si>
+  <si>
+    <t>Medicine Man</t>
+  </si>
+  <si>
+    <t>26.10.6</t>
+  </si>
+  <si>
+    <t>おれはメディソンマン
+市街地第3地区にある薬局の店長だ  
+きみ
+顔色が悪いね  
+最近仕事がつらい？  
+これ飲むか？
+一錠飲めばあと20年は働ける  
+疲れない
+悩まない
+上司にも腹が立たない  
+ただし...
+個性はなくなる
+...
+そんな顔するなよ  
+おれも飲んでる  
+ほら  
+顔色いいだろ</t>
+  </si>
+  <si>
+    <t>I'm the Medicine Man.  
+I run a pharmacy in the city's Third District.  
+Hey,
+you don't look so good.  
+Work been rough lately?  
+Want one of these?  
+Take one pill,and you'll be able to work for another twenty years.  
+No fatigue.
+No worries.
+No getting mad at your boss.  
+But...
+you'll lose your individuality.  
+...  
+Don't look at me like that.  
+I take them too.  
+See?
+I look healthy, don't I?</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>海上電波測定</t>
+  </si>
+  <si>
+    <t>Offshore Radio Measurement</t>
+  </si>
+  <si>
+    <t>電波測定のため
+三日前にCITYからここへ出張してきた
+仕事といっても
+やることはほとんどない
+ここでは魚がよく釣れる
+煮て焼いて
+酒を飲みながら測定する
+ああ
+勤務中のUFOが
+ゆっくりこちらへ近づいてきた
+どうだい
+お前も一緒に魚食ってくかい
+...
+Destroy
+...
+ですって</t>
+  </si>
+  <si>
+    <t>I came here from CITY three days ago
+to measure radio signals
+There’s not much to do as far as work goes
+The fish bite well around here
+We boil them grill them
+and take measurements over a few drinks
+Ah
+A UFO on duty
+is slowly coming this way
+Hey
+wanna come have some fish with us?
+...
+Destroy
+...
+He says.</t>
   </si>
 </sst>
 </file>
@@ -8927,12 +9021,24 @@
       <c r="Y83" s="3"/>
     </row>
     <row r="84">
-      <c r="A84" s="4"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
+      <c r="A84" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>494</v>
+      </c>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
@@ -8954,12 +9060,24 @@
       <c r="Y84" s="3"/>
     </row>
     <row r="85">
-      <c r="A85" s="4"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
+      <c r="A85" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>499</v>
+      </c>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="505">
   <si>
     <t>id</t>
   </si>
@@ -5495,6 +5495,63 @@
 Destroy
 ...
 He says.</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>EGGS</t>
+  </si>
+  <si>
+    <t>26.10.7</t>
+  </si>
+  <si>
+    <t>ここはCITYから500キロ離れた地下なのだ
+穴に入ってから随分歩いて
+ようやくたどり着いた
+ここは一体
+なんてこった
+地下に街がある
+いや街じゃない
+あれは蟻の幼虫を管理するための設備らしい
+...
+すごい空気なんだけど
+ちょっとラップするから聞いてくれ
+hey hey
+幼虫ぎっしり　成長中
+今日も地中で　培養中
+羽化まで　うかうかしてらんない
+時代は早いぜ　いっつまいめん
+boon
+……
+さ
+みんな準備はいいか
+EGGS奪還へ向けて
+侵入開始だ</t>
+  </si>
+  <si>
+    <t>This is 500 kilometers beneath CITY.
+We walked a long way after entering the tunnel
+and finally made it here.
+What is this place?
+Holy shit.
+There’s a city underground.
+No.It’s not a city.
+Apparently, those are facilities for managing ant larvae.
+...
+The atmosphere here is insane,
+but let me drop a quick rap.
+Hey, hey.
+Larvae packed tight, growing away
+Cultured underground, day after day
+No time to slack till they spread their wings
+Times move fast, it’s my main man thing
+Boon.
+...
+All right.
+Everyone ready?
+We’re taking back the EGGS.
+Begin infiltration.</t>
   </si>
 </sst>
 </file>
@@ -9099,12 +9156,24 @@
       <c r="Y85" s="3"/>
     </row>
     <row r="86">
-      <c r="A86" s="4"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
+      <c r="A86" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>504</v>
+      </c>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="511">
   <si>
     <t>id</t>
   </si>
@@ -5552,6 +5552,58 @@
 Everyone ready?
 We’re taking back the EGGS.
 Begin infiltration.</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>人間味</t>
+  </si>
+  <si>
+    <t>The Taste of Humanity</t>
+  </si>
+  <si>
+    <t>26.10.8</t>
+  </si>
+  <si>
+    <t>地球で役目を終えた魂は
+みんなこの星へ帰ってくる  
+長いこと人間をやっとると
+いろんなものがこびりつく  
+怒り
+欲
+嫉妬  
+それを一度きれいに
+取り除いてやるんじゃ  
+剥がれ落ちたものは邪鬼になる  
+なぜか
+魚の形になることが多いが  
+わしの仕事は
+それを調理して食べること  
+クセもあるし
+苦みもあるが  
+少しくらい汚れていた方が  
+人間の場合はうまい</t>
+  </si>
+  <si>
+    <t>Souls that have finished their time on Earth
+all return to this planet  
+When you've been human for a long time
+all sorts of things start clinging to you  
+Anger
+Desire
+Jealousy  
+So I clean them off
+and remove them from the soul  
+What falls away becomes Jaki  
+For some reason
+they often take the shape of fish  
+My job is
+to cook them and eat them  
+They have a peculiar taste
+and a certain bitterness  
+But when it comes to humans
+a little impurity makes them taste better</t>
   </si>
 </sst>
 </file>
@@ -9195,12 +9247,24 @@
       <c r="Y86" s="3"/>
     </row>
     <row r="87">
-      <c r="A87" s="4"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
+      <c r="A87" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>510</v>
+      </c>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="517">
   <si>
     <t>id</t>
   </si>
@@ -5604,6 +5604,58 @@
 and a certain bitterness  
 But when it comes to humans
 a little impurity makes them taste better</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>屋上銭湯</t>
+  </si>
+  <si>
+    <t>Rooftop Public Bath</t>
+  </si>
+  <si>
+    <t>26.10.9</t>
+  </si>
+  <si>
+    <t>昔は仕事が終わってから
+銭湯に行くものだったらしい
+今では朝から湯船に浸かって
+酒を呑みながら仕事したっていい
+この町では
+仕事と休暇の境界が消えているのだ
+まあ
+便利な世の中になったもんだ
+ところでお前
+今日は休みじゃなかったか？
+ああ
+そうだったな
+じゃあ何で仕事してるんだ？
+……
+ぶうううん
+銭湯の中心にあるマシーンが唸った
+こいつのおかげで湯加減はいつもいい感じ
+ビールもキンキンに冷えるのだ</t>
+  </si>
+  <si>
+    <t>Apparently, people used to go to the public bath
+after finishing work
+These days, you can soak in the bath from early morning
+and work while drinking beer
+In this city
+the line between work and leisure has disappeared
+Well
+what a convenient world we live in
+By the way
+weren't you supposed to be off today?
+Oh yeah
+that's right
+Then why are you working?
+……
+Brrrrrrrr
+The machine at the center of the bathhouse hummed
+Thanks to this thing, the bathwater is always just right
+And the beer stays ice-cold too</t>
   </si>
 </sst>
 </file>
@@ -9286,12 +9338,24 @@
       <c r="Y87" s="3"/>
     </row>
     <row r="88">
-      <c r="A88" s="4"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
+      <c r="A88" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>516</v>
+      </c>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="527">
   <si>
     <t>id</t>
   </si>
@@ -5656,6 +5656,126 @@
 The machine at the center of the bathhouse hummed
 Thanks to this thing, the bathwater is always just right
 And the beer stays ice-cold too</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>ABURA</t>
+  </si>
+  <si>
+    <t>26.10.11</t>
+  </si>
+  <si>
+    <t>仕事終わりの帰り道
+魚屋に寄る
+鯵と鯖
+一枚ずつもらえる？
+ちょっとこの火鉢で炙らせてもらうよ
+ジュウと
+勢いよく白い煙が立つ
+ABURA
+素敵だ
+頭上ではドローンが飛び
+配送ロボが忙しそうに走っている
+ここは昭和かそれとも未来か
+まあどっちでもいい
+今日も私は魚を買って帰るのだ
+……
+ん
+意味って？
+ないよ
+日記みたいなもんだから
+そう思って読んでくれたら
+おじさん嬉しい</t>
+  </si>
+  <si>
+    <t>On my way home from work
+I stop by the fish shop
+Horse mackerel and mackerel
+Can I have one of each?
+Mind if I grill them over this charcoal brazier?
+Sizzle
+A thick cloud of white smoke rises
+ABURA
+Beautiful
+Overhead, drones are flying
+Delivery robots are rushing around
+Is this the Showa era or the future?
+Well, either way is fine
+Today, once again, I buy some fish and head home
+……
+Hm
+What's the meaning?
+There isn't one
+It's just like a diary
+If you read it that way
+It would make this old man happy</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>虫蜜電力</t>
+  </si>
+  <si>
+    <t>Insect Honey Power</t>
+  </si>
+  <si>
+    <t>最近はどこの会社も電力不足だ
+コンピューターの数が増えすぎたらしい
+そこで開発されたのが昆虫発電
+昆虫が取り込んだ養分を
+電力に変換する仕組みだ
+これがなかなか優秀でね
+餌さえ与えておけば
+一日中働いてくれる
+おまけに副産物の虫蜜がうまい
+私は毎朝パンにつけて食べている
+昔は駅前にオフィスを建てたものだが
+今では昆虫の生息地に
+オフィスを建てるのが常識になった
+だからこの辺りは
+森の中にビルが並んでいる
+おい
+また一棟増えてないか？
+ああ
+昨日から新しい群れが来たんだ
+なるほど
+ビルだけに
+ビートルさまさまってことか
+...
+そういや
+あいつらの餌代
+俺たちの給料より高いらしいぞ</t>
+  </si>
+  <si>
+    <t>These days, every company is running short on electricity
+Apparently, there are just too many computers
+That's why insect-powered electricity was developed
+It's a system that converts the nutrients
+absorbed by insects into electricity
+And it's surprisingly efficient
+As long as you feed them
+they'll work all day long
+As a bonus, the insect honey they produce is delicious
+I spread it on my bread every morning
+In the old days, offices were built near train stations
+But nowadays, it's common practice
+to build offices wherever insects live
+That's why around here
+office buildings stand scattered throughout the forest
+Hey
+Hasn't another building gone up?
+Yeah
+A new swarm arrived yesterday
+I see
+Well, when it comes to buildings
+we've got the beetles to thank
+...
+Come to think of it
+I heard their food costs
+more than our salaries</t>
   </si>
 </sst>
 </file>
@@ -9377,12 +9497,24 @@
       <c r="Y88" s="3"/>
     </row>
     <row r="89">
-      <c r="A89" s="4"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
+      <c r="A89" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>521</v>
+      </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
@@ -9404,12 +9536,24 @@
       <c r="Y89" s="3"/>
     </row>
     <row r="90">
-      <c r="A90" s="4"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
+      <c r="A90" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>526</v>
+      </c>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="533">
   <si>
     <t>id</t>
   </si>
@@ -5776,6 +5776,52 @@
 Come to think of it
 I heard their food costs
 more than our salaries</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>謎球根</t>
+  </si>
+  <si>
+    <t>Mysterious Bulb</t>
+  </si>
+  <si>
+    <t>26.10.14</t>
+  </si>
+  <si>
+    <t>おい
+そいつをこっちに運んできてくれ
+ああ
+中はだいぶ成熟してきているぞ
+いいぞ
+今日は何個だ？
+百二十七
+昨日より多いな
+ああ
+最近は空の連中もよく食うからな
+……
+おい
+一個開きかけてるぞ
+見るな
+まだ早い</t>
+  </si>
+  <si>
+    <t>Hey
+bring that one over here
+Yeah
+the inside's getting pretty mature now
+Good
+How many today?
+127
+More than yesterday
+Yeah
+those guys up in the sky have been eating a lot lately
+……
+Hey
+one of them's starting to open
+Don't look
+It's not time yet</t>
   </si>
 </sst>
 </file>
@@ -9575,12 +9621,24 @@
       <c r="Y90" s="3"/>
     </row>
     <row r="91">
-      <c r="A91" s="4"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
+      <c r="A91" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>532</v>
+      </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="539">
   <si>
     <t>id</t>
   </si>
@@ -5796,7 +5796,7 @@
 中はだいぶ成熟してきているぞ
 いいぞ
 今日は何個だ？
-百二十七
+127
 昨日より多いな
 ああ
 最近は空の連中もよく食うからな
@@ -5822,6 +5822,48 @@
 one of them's starting to open
 Don't look
 It's not time yet</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>次元横断歩道</t>
+  </si>
+  <si>
+    <t>Interdimensional Crosswalk</t>
+  </si>
+  <si>
+    <t>26.10.15</t>
+  </si>
+  <si>
+    <t>次元を移動するとき
+必ずこの横断歩道を渡る
+ここでは色々な人とすれ違う
+どこの次元から来たのか
+わからない奴もいる
+会話はできない
+声を出しても届かないのだ
+目が合ってしまった
+なんだか見覚えのある顔だ
+……
+あ
+俺だ
+ずいぶん老けたな</t>
+  </si>
+  <si>
+    <t>Whenever we travel between dimensions
+We must cross this crosswalk
+All kinds of people pass each other here
+Some of them
+I have no idea which dimension they came from
+We can't have conversations
+Even if we speak
+our voices never reach each other
+Our eyes met That face looks strangely familiar
+……
+Oh
+That's me
+I've gotten pretty old</t>
   </si>
 </sst>
 </file>
@@ -9660,12 +9702,24 @@
       <c r="Y91" s="3"/>
     </row>
     <row r="92">
-      <c r="A92" s="4"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
+      <c r="A92" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>538</v>
+      </c>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="545">
   <si>
     <t>id</t>
   </si>
@@ -5864,6 +5864,62 @@
 Oh
 That's me
 I've gotten pretty old</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>水と後悔</t>
+  </si>
+  <si>
+    <t>Water and Regret</t>
+  </si>
+  <si>
+    <t>26.10.16</t>
+  </si>
+  <si>
+    <t>ゴボゴボ
+朝一番のジュースはうまい
+これは質量分析計
+君がどんな成分でできているかを
+測る装置なのさ
+今日も君から採った赤い成分を測定する
+ウィーン
+カタカタ
+ほら
+炭素
+水素
+酸素
+嫉妬
+後悔
+……
+おや
+昨日より希望が減っているな
+まあ
+人間なんて
+だいたい水と後悔でできているのだ</t>
+  </si>
+  <si>
+    <t>Gurgle, gurgle
+Nothing beats a glass of juice first thing in the morning
+This is a mass spectrometer
+It's a machine that tells us
+what you're made of
+Today, I'll analyze the red substance I collected from you again
+Whirrr
+Clack clack
+See?
+Carbon
+Hydrogen
+Oxygen
+Jealousy
+Regret
+...
+Oh?
+Your hope levels are lower than yesterday
+Well
+Humans are, after all,
+mostly made of water and regret</t>
   </si>
 </sst>
 </file>
@@ -9741,12 +9797,24 @@
       <c r="Y92" s="3"/>
     </row>
     <row r="93">
-      <c r="A93" s="4"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
+      <c r="A93" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="557">
   <si>
     <t>id</t>
   </si>
@@ -5583,7 +5583,7 @@
 クセもあるし
 苦みもあるが  
 少しくらい汚れていた方が  
-人間の場合はうまい</t>
+美味いのだ</t>
   </si>
   <si>
     <t>Souls that have finished their time on Earth
@@ -5920,6 +5920,162 @@
 Well
 Humans are, after all,
 mostly made of water and regret</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>ツナわかるよな</t>
+  </si>
+  <si>
+    <t>Tuna, You Know the Deal</t>
+  </si>
+  <si>
+    <t>26.10.19</t>
+  </si>
+  <si>
+    <t>地上に住めなくなって
+もう何年になるんだろうな
+海底生活にもすっかり慣れたが
+食事だけはどうにも飽きてきた
+毎日サバ、イワシ、ツナ
+たまに海底虫
+レシピを変えたところで
+結局いつも同じ味だ
+しかし
+よく考えたら妙な話だよな
+海底に会社まで作って
+地上はフィジカルAIが洗浄してくれている
+俺たちは毎日ここで仕事して
+飯食って
+寝て
+本当に地上へ戻れる日なんて来るのかね
+……
+まあ
+こういう時はラップだな
+ツナ
+わかるよな
+油少なめ
+舌平目
+サバサバすんなよ
+まだまだ海底
+上がれぬ地上に
+届けよ低音
+ウンズッタッタ
+ウンウンズ
+油少なめ
+舌平目</t>
+  </si>
+  <si>
+    <t>How many years has it been
+since we could no longer live on the surface?
+I've gotten used to life under the sea
+but the food is getting pretty old
+Mackerel, sardines, tuna every day
+the occasional deep-sea bug
+No matter how we change the recipes
+it all ends up tasting the same
+But
+when you think about it, it's pretty strange
+We've even built companies under the sea
+while Physical AI cleans up the surface for us
+We work here every day
+eat
+and sleep
+Will we ever really get to return to the surface?
+……
+Well
+times like these call for a little rap
+Tuna
+you know the deal, don't ya?
+Go easy on the oil
+bring on the sole
+Don't get all mackerel-moody
+we're still down in the deep
+To the surface we can't reach
+let the bass go deep
+Oom-zut-ta-ta
+Oom-oom-z
+Go easy on the oil
+bring on the sole</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>いつから人間</t>
+  </si>
+  <si>
+    <t>Since Becoming Human</t>
+  </si>
+  <si>
+    <t>26.10.20</t>
+  </si>
+  <si>
+    <t>いらっしゃいませ
+あら
+最近ロボット殿がまた増えてきましたね
+最初はどうなるかと思ったけど
+母がいた時から比べて
+随分この辺りも様変わりしたわ
+昔は人間のお客さんばかりだったのよ
+今じゃ半分以上が機械のお客さん
+最初の頃は大変だったわ
+油を出せだの
+電気を飲ませろだの
+寿司屋なのにねえ
+でも最近のロボット殿は
+人間と同じものを食べるのよ
+味までわかるんですって
+便利な時代になったものね
+あら
+お客さん
+おかわりですか？
+はいはい
+いつものですね
+ところで
+お客さんは
+いつから人間になられたんです？
+あら
+そうでしたか
+もう三十年も前になるんですね
+昔は立派な鉄の頭をしてらしたのに
+……
+そういえば私も最近
+母に似てきたって言われるんですよ
+ふふ</t>
+  </si>
+  <si>
+    <t>Welcome
+Oh my
+We've been seeing more robot gentlemen around here lately
+At first I wasn't sure how things would turn out
+But compared to when my mother was around
+This neighborhood has changed so much
+Back then almost all our customers were human
+Nowadays more than half of them are machines
+It was quite a struggle in the beginning
+Some demanded oil
+Others wanted electricity to drink
+And this is a sushi restaurant
+But these days robot gentlemen
+Eat the same food as humans
+They can even taste it, apparently
+What a convenient age we live in
+Oh
+Would you like another serving?
+Of course
+The usual, then
+By the way
+When did you become human?
+Oh
+I see
+So it's been thirty years already
+You used to have such a fine iron head
+...
+Come to think of it, lately
+People have been telling me I'm starting to look more like my mother
+Hehe</t>
   </si>
 </sst>
 </file>
@@ -9836,12 +9992,24 @@
       <c r="Y93" s="3"/>
     </row>
     <row r="94">
-      <c r="A94" s="4"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
+      <c r="A94" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>550</v>
+      </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
@@ -9863,12 +10031,24 @@
       <c r="Y94" s="3"/>
     </row>
     <row r="95">
-      <c r="A95" s="4"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
+      <c r="A95" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="563">
   <si>
     <t>id</t>
   </si>
@@ -6076,6 +6076,61 @@
 Come to think of it, lately
 People have been telling me I'm starting to look more like my mother
 Hehe</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>胞子日和</t>
+  </si>
+  <si>
+    <t>A Fine Day for Spores</t>
+  </si>
+  <si>
+    <t>26.10.21</t>
+  </si>
+  <si>
+    <t>んーまっ
+もう少し湿度を上げちゃおうか
+んーまっ
+そうそう
+徐々に開いてきた
+いいねえ
+ここは菌体研究所
+培養に必要な水と空気が
+唯一残っているこの場所が
+僕のオフィスさ
+昔はもっと簡単に培養できたんだけどね
+最近は空気が乾燥しちゃって
+なかなか育たないんだ
+んーまっ
+お
+胞子が出てきた
+いいぞ
+...
+世界にばら撒く日も近い</t>
+  </si>
+  <si>
+    <t>Mmm-ah
+Let's raise the humidity a little more
+Mmm-ah
+That's it
+Slowly starting to open up
+Looking good
+This is the Fungal Research Laboratory
+This place
+where the water and air needed for cultivation
+are the only ones left
+is my office
+Cultivating used to be much easier back then
+But lately the air has gotten so dry
+that nothing grows very well
+Mmm-ah
+Oh
+The spores are coming out
+Excellent
+...
+The day I scatter them across the world is almost here</t>
   </si>
 </sst>
 </file>
@@ -10070,12 +10125,24 @@
       <c r="Y95" s="3"/>
     </row>
     <row r="96">
-      <c r="A96" s="4"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
+      <c r="A96" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>562</v>
+      </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="568">
   <si>
     <t>id</t>
   </si>
@@ -6131,6 +6131,57 @@
 Excellent
 ...
 The day I scatter them across the world is almost here</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t>FICTORY</t>
+  </si>
+  <si>
+    <t>26.10.22</t>
+  </si>
+  <si>
+    <t>ここはFictory
+火星の三つ隣の星を
+急いで開拓することになった
+この星にはまだ何もない
+まずはベルトコンベアを設置する
+それからあいつを運んでくる
+地中に埋めて
+たっぷり水をやる
+そうすると
+勝手に卵を産み始めるから
+それを使って養殖場をつくる
+それから...
+おい
+君は話し過ぎなんだ
+誰かに聞かれたらどうするんだ
+……
+すみません
+ここはFictoryなので
+つい</t>
+  </si>
+  <si>
+    <t>This is Fictory
+We've been ordered to urgently develop
+a planet three planets over from Mars
+There's still nothing on this planet
+First we install the conveyor belts
+Then we bring that thing over
+Bury it underground
+and give it plenty of water
+Once we do that
+it starts laying eggs on its own
+We use those eggs to build a breeding farm
+And then...
+Hey
+You talk too much
+What if someone overhears you?
+……
+Sorry
+It's just that this is Fictory
+I couldn't help myself</t>
   </si>
 </sst>
 </file>
@@ -10164,12 +10215,24 @@
       <c r="Y96" s="3"/>
     </row>
     <row r="97">
-      <c r="A97" s="4"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
+      <c r="A97" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>567</v>
+      </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="574">
   <si>
     <t>id</t>
   </si>
@@ -6182,6 +6182,62 @@
 Sorry
 It's just that this is Fictory
 I couldn't help myself</t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t>鮭教</t>
+  </si>
+  <si>
+    <t>Salmon Cult</t>
+  </si>
+  <si>
+    <t>26.10.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ぐわんぐわんぐわん
+昭和の街中にそびえ立つマンションの屋上では
+いつもこの音が鳴っている
+何をしているかだって？
+サーモンを捌いて
+切り身を流しているのだ
+この宗教施設ではそういうしきたり
+夜8時になると信者たちが集まって
+黙々とサーモンを捌く
+切り身はベルトコンベヤーを流れる
+あまりの不思議な光景なので
+たまにUFOが
+社会見学に来るらしい
+...
+あ、あれが教科書に載ってるっていう
+そう
+あの人達が
+かの有名な鮭教の狂人達よ
+</t>
+  </si>
+  <si>
+    <t>On the rooftop of an apartment building
+towering over a Showa-era city
+this sound can always be heard
+What are they doing up there?
+They're cutting up salmon
+and sending the fillets down the line
+That's simply the custom
+at this religious facility
+Every night at 8
+the believers gather
+and silently cut up salmon
+The fillets travel along a conveyor belt
+The sight is so bizarre that
+UFOs occasionally come
+on field trips to observe it
+...
+Oh, so those are the people
+we read about in our textbooks
+That's right
+Those are
+the infamous lunatics of the Salmon Cult</t>
   </si>
 </sst>
 </file>
@@ -10254,12 +10310,24 @@
       <c r="Y97" s="3"/>
     </row>
     <row r="98">
-      <c r="A98" s="4"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
+      <c r="A98" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>573</v>
+      </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -6217,24 +6217,21 @@
 </t>
   </si>
   <si>
-    <t>On the rooftop of an apartment building
-towering over a Showa-era city
-this sound can always be heard
+    <t>Gwan gwan gwan
+On the rooftop of an apartment building
+towering over a Showa-era city this sound can always be heard
 What are they doing up there?
 They're cutting up salmon
 and sending the fillets down the line
-That's simply the custom
-at this religious facility
-Every night at 8
-the believers gather
+That's simply the custom at this religious facility
+Every night at 8 the believers gather
 and silently cut up salmon
 The fillets travel along a conveyor belt
 The sight is so bizarre that
 UFOs occasionally come
 on field trips to observe it
 ...
-Oh, so those are the people
-we read about in our textbooks
+Oh, so those are the people we read about in our textbooks
 That's right
 Those are
 the infamous lunatics of the Salmon Cult</t>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="580">
   <si>
     <t>id</t>
   </si>
@@ -6235,6 +6235,57 @@
 That's right
 Those are
 the infamous lunatics of the Salmon Cult</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>第三架線</t>
+  </si>
+  <si>
+    <t>The Third Cable Line</t>
+  </si>
+  <si>
+    <t>26.10.26</t>
+  </si>
+  <si>
+    <t>今朝入ったばかりの肉
+マグロに見えるけど
+陸で育てば牛
+海で育てばマグロ
+違いは？
+第一架線で来れば牛肉
+第二架線ならマグロだ
+この肉は？
+店主は水路を歩く獣人を指差した
+……
+獣人か
+最近あまり見かけないな
+ああ
+第三架線が開通したからな
+ガタンゴトン
+今日も頭上を
+黄色い窓の車両が通り過ぎていく</t>
+  </si>
+  <si>
+    <t>Fresh meat
+Just arrived this morning
+Looks like tuna to me
+Raised on land, it's beef
+Raised in the sea, it's tuna
+What's the difference?
+If it comes on Line One, it's beef
+Line Two, it's tuna
+What about this meat?
+The shopkeeper pointed at a beastman walking through the canal
+...
+A beastman, huh
+Haven't seen many of them lately
+Yeah
+Ever since Line Three opened
+Clackety-clack
+Another train with yellow-lit windows
+passes overhead today</t>
   </si>
 </sst>
 </file>
@@ -10346,12 +10397,24 @@
       <c r="Y98" s="3"/>
     </row>
     <row r="99">
-      <c r="A99" s="4"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
+      <c r="A99" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>579</v>
+      </c>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="586">
   <si>
     <t>id</t>
   </si>
@@ -6286,6 +6286,79 @@
 Clackety-clack
 Another train with yellow-lit windows
 passes overhead today</t>
+  </si>
+  <si>
+    <t>099</t>
+  </si>
+  <si>
+    <t>ドッキング日和</t>
+  </si>
+  <si>
+    <t>A Fine Day for Docking</t>
+  </si>
+  <si>
+    <t>26.10.28</t>
+  </si>
+  <si>
+    <t>課長
+赤い方から連絡入りました
+お
+そろそろか
+はい
+脱皮が始まったそうです
+よし
+ドッキング準備だ
+青い甲殻類がゆっくりと脚を伸ばす
+宇宙船同士が近づき
+巨大なハサミが絡み合う
+ガシャン
+おお
+今年も無事に繋がったな
+課長
+毎年思うんですが
+これって交尾ですよね
+まあ
+そういうことになるな
+我々の仕事は
+彼らの繁殖を手伝うことだ
+ところで課長
+去年生まれた子供は
+ああ
+あそこで働いてるよ
+……
+ドッキングどっきどき
+脱皮でハッピー
+今日も宇宙は平和なのだ</t>
+  </si>
+  <si>
+    <t>Boss
+We just heard from the red one
+Oh
+Is it time already?
+Yes
+Apparently, it's started molting
+Alright
+Prepare for docking
+The blue crustacean slowly stretches out its legs
+The two spaceships approach each other
+Their enormous claws intertwine
+CLANG
+Oh
+Another successful connection this year
+Boss
+I think about this every year
+But isn't this basically mating?
+Well
+I suppose you could call it that
+Our job is to help them reproduce
+By the way, Boss
+What happened to the baby born last year?
+Oh
+It's working over there
+……
+Docking, how shocking
+Molting, how rocking
+Another peaceful day in the universe</t>
   </si>
 </sst>
 </file>
@@ -10436,12 +10509,24 @@
       <c r="Y99" s="3"/>
     </row>
     <row r="100">
-      <c r="A100" s="4"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
+      <c r="A100" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>585</v>
+      </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="592">
   <si>
     <t>id</t>
   </si>
@@ -6359,6 +6359,63 @@
 Docking, how shocking
 Molting, how rocking
 Another peaceful day in the universe</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>長湯厳禁</t>
+  </si>
+  <si>
+    <t>No Prolonged Soaking</t>
+  </si>
+  <si>
+    <t>26.10.30</t>
+  </si>
+  <si>
+    <t>雪が降り続く厳冬の季節には
+この風呂がしみる
+温泉？
+違う
+栄養ドリンクだ
+飲む？
+違う
+肌から挿れる
+人間というのは
+普通に進化しても今のようにはならない
+昔どこかでだれかに挿れられている
+まあ
+誰が作ったのかはよいとして
+長湯は禁物だ
+体が発酵する
+人間じゃなくなっちまう
+……
+おい
+おっさん
+発酵してないか？</t>
+  </si>
+  <si>
+    <t>When the snow keeps falling
+through the bitter winter
+Nothing feels better than this bath
+A hot spring?
+No
+It's an energy drink
+You drink it?
+No
+You absorb it through your skin
+Humans, you see
+Could never have become what they are today through natural evolution alone
+Long ago somewhere someone injected something into us
+Well
+never mind who made us
+Just don't stay in too long
+Your body will start to ferment
+And you won't be human anymore
+...
+Hey
+old man
+Aren't you fermenting?</t>
   </si>
 </sst>
 </file>
@@ -10548,12 +10605,24 @@
       <c r="Y100" s="3"/>
     </row>
     <row r="101">
-      <c r="A101" s="4"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
+      <c r="A101" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>591</v>
+      </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="598">
   <si>
     <t>id</t>
   </si>
@@ -6416,6 +6416,68 @@
 Hey
 old man
 Aren't you fermenting?</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>王家の自販機</t>
+  </si>
+  <si>
+    <t>Royal Vending Machine</t>
+  </si>
+  <si>
+    <t>26.10.31</t>
+  </si>
+  <si>
+    <t>実はピラミッドの地下には
+ハンバーガーの自販機がある
+人間たちは
+我々ミイラが何千年も保管されていたと思っているらしい
+違う
+ちゃんと食べているのだ
+朝は決まった時間に起きて
+軽くストレッチ
+ウォーキングをして読書をする
+健康には気を遣っている
+そして最後にこいつを食べれば
+はい優勝
+人間たちが調査に来る時だけは
+仮死モードに入る
+あいつら
+我々が動くと大騒ぎするからな
+誰がハンバーガーを供給してくれるのかって
+CITYの人間だ
+...
+あいつら
+昔からこういう商売だけは
+本当にうまいんだ</t>
+  </si>
+  <si>
+    <t>There are actually
+hamburger vending machines
+beneath the pyramids
+Humans seem to think
+we mummies have been preserved for thousands of years
+Wrong
+We've been eating just fine
+Every morning I wake up at the same time
+and do some light stretching
+I go for a walk and read a book
+I take good care of my health
+And finally
+I eat one of these
+That's a perfect morning right there
+Only when humans come to investigate
+do we switch into suspended animation mode
+Those guys
+make such a fuss whenever we move
+Who's supplying the hamburgers, you ask?
+The people of CITY
+...
+Those guys
+They've always been
+really good at this kind of business</t>
   </si>
 </sst>
 </file>
@@ -10644,12 +10706,24 @@
       <c r="Y101" s="3"/>
     </row>
     <row r="102">
-      <c r="A102" s="4"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
+      <c r="A102" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>597</v>
+      </c>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="604">
   <si>
     <t>id</t>
   </si>
@@ -6478,6 +6478,66 @@
 Those guys
 They've always been
 really good at this kind of business</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>トマト稟議</t>
+  </si>
+  <si>
+    <t>Tomato Approval Request</t>
+  </si>
+  <si>
+    <t>26.11.1</t>
+  </si>
+  <si>
+    <t>トマト型のヘルメットを買った
+なぜか無性に欲しくなったのだ
+同僚には笑われたが
+まあ気にしない
+そもそも普通の人間は
+こんなものを被ろうと思わない
+きっと頭の中がおかしいのだ
+では少し覗いてみよう
+……
+カタカタ
+おい
+まだ帰らないのか？
+ああ
+昨日からずっと残業だよ
+ところで
+トマトの件、誰が承認した？
+知らん
+部長じゃないの？
+部長なら先週から休んでるぞ
+……
+カタカタ
+今日も正常に異常なのだ</t>
+  </si>
+  <si>
+    <t>I bought a tomato-shaped helmet
+For some reason, I desperately wanted one
+My coworkers laughed at me
+but I didn't really care
+After all, no normal person
+would ever think of wearing something like this
+There must be something wrong inside my head
+Well then, let's take a little look
+……
+Clack clack
+Hey
+aren't you going home yet?
+Nah
+I've been working overtime since yesterday
+By the way
+who approved the tomato thing?
+No idea
+Wasn't it the manager?
+The manager's been off since last week
+……
+Clack clack
+Another perfectly abnormal day</t>
   </si>
 </sst>
 </file>
@@ -10745,12 +10805,24 @@
       <c r="Y102" s="3"/>
     </row>
     <row r="103">
-      <c r="A103" s="4"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
+      <c r="A103" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>603</v>
+      </c>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
